--- a/outputs/q3/q3_box_deliveries.xlsx
+++ b/outputs/q3/q3_box_deliveries.xlsx
@@ -489,7 +489,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S014-FOD-01</t>
+          <t>S006-MED-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -499,17 +499,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>S014</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1275.477572494324</v>
+        <v>935.5024303951484</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>7200</v>
+        <v>3600</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3600</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>0</v>
@@ -518,7 +521,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S014-WAT-01</t>
+          <t>S006-WAT-03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -528,16 +531,13 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>S014</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1275.477572494324</v>
+        <v>935.5024303951484</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>3600</v>
-      </c>
-      <c r="F3" t="n">
         <v>3600</v>
       </c>
       <c r="G3" s="2" t="n">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S002-MED-01</t>
+          <t>S006-WAT-01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -560,11 +560,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>3561.095990967302</v>
+        <v>2505.450960754921</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>3600</v>
@@ -573,7 +573,7 @@
         <v>3600</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>0</v>
@@ -582,7 +582,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S004-MED-01</t>
+          <t>S006-WAT-02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -592,20 +592,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>S004</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>4038.626814774521</v>
+        <v>2505.450960754921</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>7200</v>
-      </c>
-      <c r="F5" t="n">
-        <v>7200</v>
+        <v>3600</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>0</v>
@@ -614,30 +611,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S004-WAT-01</t>
+          <t>S008-FOD-01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Q2-002</t>
+          <t>Q2-003</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>S004</t>
+          <t>S008</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>4038.626814774521</v>
+        <v>6160.295384496833</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>7200</v>
-      </c>
-      <c r="F6" t="n">
-        <v>7200</v>
+        <v>10800</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>0</v>
@@ -646,7 +640,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S014-MED-01</t>
+          <t>S008-MED-01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -656,20 +650,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>S014</t>
+          <t>S008</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>2586.240572494324</v>
+        <v>6160.295384496833</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>7200</v>
       </c>
       <c r="F7" t="n">
-        <v>3600</v>
+        <v>7200</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>0</v>
@@ -678,7 +672,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S011-FOD-01</t>
+          <t>S008-WAT-01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -688,17 +682,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>S011</t>
+          <t>S008</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>3641.992840940934</v>
+        <v>6160.295384496833</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>14400</v>
+        <v>7200</v>
+      </c>
+      <c r="F8" t="n">
+        <v>7200</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>0</v>
@@ -707,30 +704,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S011-MED-01</t>
+          <t>S009-FOD-01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Q2-003</t>
+          <t>Q2-004</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>S011</t>
+          <t>S009</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>3641.992840940934</v>
+        <v>6275.503615915664</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>10800</v>
-      </c>
-      <c r="F9" t="n">
-        <v>10800</v>
+        <v>14400</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>0</v>
@@ -739,7 +733,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S013-FOD-01</t>
+          <t>S009-WAT-01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -749,17 +743,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>S013</t>
+          <t>S009</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>3046.716202171554</v>
+        <v>6275.503615915664</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>7200</v>
+        <v>10800</v>
+      </c>
+      <c r="F10" t="n">
+        <v>10800</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>0</v>
@@ -768,27 +765,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S010-FOD-01</t>
+          <t>S001-HYG-01</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Q2-004</t>
+          <t>Q2-005</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>S010</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>3453.383856901935</v>
+        <v>1248.26953866458</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>7200</v>
+        <v>10800</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>0</v>
@@ -797,7 +794,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S002-FOD-01</t>
+          <t>S001-MED-01</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -807,17 +804,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>3202.927150049232</v>
+        <v>1248.26953866458</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>7200</v>
+        <v>3600</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3600</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>0</v>
@@ -826,30 +826,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S009-WAT-01</t>
+          <t>S001-WAT-03</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Q2-006</t>
+          <t>Q2-005</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>S009</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>6248.219615915665</v>
+        <v>1248.26953866458</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>10800</v>
-      </c>
-      <c r="F13" t="n">
-        <v>10800</v>
+        <v>3600</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>0</v>
@@ -858,27 +855,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S002-FOD-02</t>
+          <t>S001-WAT-04</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Q2-006</t>
+          <t>Q2-005</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>6648.208760086039</v>
+        <v>1248.26953866458</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>7200</v>
+        <v>3600</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>0</v>
@@ -887,27 +884,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S007-HYG-01</t>
+          <t>S001-WAT-06</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Q2-007</t>
+          <t>Q2-005</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>S007</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>1131.143699490212</v>
+        <v>1248.26953866458</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>10800</v>
+        <v>3600</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>0</v>
@@ -916,26 +913,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S007-WAT-01</t>
+          <t>S001-WAT-07</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Q2-007</t>
+          <t>Q2-005</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>S007</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1131.143699490212</v>
+        <v>1248.26953866458</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>3600</v>
-      </c>
-      <c r="F16" t="n">
         <v>3600</v>
       </c>
       <c r="G16" s="2" t="n">
@@ -948,30 +942,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S006-MED-01</t>
+          <t>S001-WAT-08</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Q2-008</t>
+          <t>Q2-005</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>935.5024303951484</v>
+        <v>1248.26953866458</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>3600</v>
       </c>
-      <c r="F17" t="n">
-        <v>3600</v>
-      </c>
       <c r="G17" s="2" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>0</v>
@@ -980,27 +971,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S006-WAT-03</t>
+          <t>S008-HYG-01</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Q2-008</t>
+          <t>Q2-006</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S008</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>935.5024303951484</v>
+        <v>5071.887384496832</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>3600</v>
+        <v>14400</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>0</v>
@@ -1009,30 +1000,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S013-MED-01</t>
+          <t>S008-WAT-02</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Q2-009</t>
+          <t>Q2-006</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>S013</t>
+          <t>S008</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>1119.837202171553</v>
+        <v>5071.887384496832</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>3600</v>
-      </c>
-      <c r="F19" t="n">
-        <v>3600</v>
+        <v>7200</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>0</v>
@@ -1041,30 +1029,30 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S010-MED-01</t>
+          <t>S005-WAT-01</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Q2-009</t>
+          <t>Q2-007</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>S010</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>1556.504856901935</v>
+        <v>5099.414896432129</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>3600</v>
+        <v>10800</v>
       </c>
       <c r="F20" t="n">
-        <v>3600</v>
+        <v>10800</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>0</v>
@@ -1073,30 +1061,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S010-WAT-01</t>
+          <t>S007-FOD-01</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Q2-009</t>
+          <t>Q2-007</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>S010</t>
+          <t>S007</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>1556.504856901935</v>
+        <v>5844.92073817196</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>3600</v>
-      </c>
-      <c r="F21" t="n">
-        <v>3600</v>
+        <v>7200</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>0</v>
@@ -1105,30 +1090,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S009-MED-01</t>
+          <t>S003-FOD-01</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Q2-010</t>
+          <t>Q2-008</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>S009</t>
+          <t>S003</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>5524.466615915664</v>
+        <v>5936.767674802334</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>10800</v>
       </c>
-      <c r="F22" t="n">
-        <v>10800</v>
-      </c>
       <c r="G22" s="2" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>0</v>
@@ -1137,30 +1119,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S005-MED-01</t>
+          <t>S003-FOD-02</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Q2-010</t>
+          <t>Q2-008</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S003</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>6067.239842044882</v>
+        <v>5936.767674802334</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>10800</v>
       </c>
-      <c r="F23" t="n">
-        <v>10800</v>
-      </c>
       <c r="G23" s="2" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>0</v>
@@ -1169,27 +1148,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S005-WAT-03</t>
+          <t>S003-HYG-01</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Q2-010</t>
+          <t>Q2-008</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S003</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>6067.239842044882</v>
+        <v>5936.767674802334</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>10800</v>
+        <v>14400</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>0</v>
@@ -1198,12 +1177,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S003-MED-01</t>
+          <t>S003-WAT-02</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Q2-011</t>
+          <t>Q2-008</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1212,16 +1191,13 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>5720.334972714344</v>
+        <v>5936.767674802334</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>7200</v>
       </c>
-      <c r="F25" t="n">
-        <v>7200</v>
-      </c>
       <c r="G25" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>0</v>
@@ -1230,30 +1206,27 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S015-MED-01</t>
+          <t>S003-WAT-03</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Q2-011</t>
+          <t>Q2-008</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>S015</t>
+          <t>S003</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>6203.524715269023</v>
+        <v>5936.767674802334</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>7200</v>
       </c>
-      <c r="F26" t="n">
-        <v>7200</v>
-      </c>
       <c r="G26" s="2" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>0</v>
@@ -1262,30 +1235,27 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S015-WAT-01</t>
+          <t>S003-WAT-04</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Q2-011</t>
+          <t>Q2-008</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>S015</t>
+          <t>S003</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>6203.524715269023</v>
+        <v>5936.767674802334</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>10800</v>
-      </c>
-      <c r="F27" t="n">
-        <v>10800</v>
+        <v>7200</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>0</v>
@@ -1294,27 +1264,27 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S001-HYG-01</t>
+          <t>S014-FOD-01</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Q2-012</t>
+          <t>Q2-009</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S014</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>3320.57753866458</v>
+        <v>1272.761572494324</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>10800</v>
+        <v>7200</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>0</v>
@@ -1323,21 +1293,21 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>S001-MED-01</t>
+          <t>S014-WAT-01</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Q2-012</t>
+          <t>Q2-009</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S014</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>3320.57753866458</v>
+        <v>1272.761572494324</v>
       </c>
       <c r="E29" s="2" t="n">
         <v>3600</v>
@@ -1346,7 +1316,7 @@
         <v>3600</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>0</v>
@@ -1355,27 +1325,30 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S001-WAT-03</t>
+          <t>S003-MED-01</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Q2-012</t>
+          <t>Q2-010</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S003</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>3320.57753866458</v>
+        <v>5753.919972714344</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>3600</v>
+        <v>7200</v>
+      </c>
+      <c r="F30" t="n">
+        <v>7200</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>0</v>
@@ -1384,27 +1357,30 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S001-WAT-04</t>
+          <t>S015-MED-01</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Q2-012</t>
+          <t>Q2-010</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S015</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>3320.57753866458</v>
+        <v>6237.109715269023</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>3600</v>
+        <v>7200</v>
+      </c>
+      <c r="F31" t="n">
+        <v>7200</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>0</v>
@@ -1413,27 +1389,30 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S001-WAT-06</t>
+          <t>S015-WAT-01</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Q2-012</t>
+          <t>Q2-010</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S015</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>3320.57753866458</v>
+        <v>6237.109715269023</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>3600</v>
+        <v>10800</v>
+      </c>
+      <c r="F32" t="n">
+        <v>10800</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>0</v>
@@ -1442,27 +1421,27 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>S001-WAT-07</t>
+          <t>S004-WAT-02</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Q2-012</t>
+          <t>Q2-011</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S004</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>3320.57753866458</v>
+        <v>4189.977485198306</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>3600</v>
+        <v>7200</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>0</v>
@@ -1471,7 +1450,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>S001-WAT-08</t>
+          <t>S002-FOD-01</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1481,17 +1460,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>3320.57753866458</v>
+        <v>3244.337150049232</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>3600</v>
+        <v>7200</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>0</v>
@@ -1500,27 +1479,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>S007-WAT-02</t>
+          <t>S002-FOD-02</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Q2-013</t>
+          <t>Q2-012</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>S007</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>1101.143699490212</v>
+        <v>3244.337150049232</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>3600</v>
+        <v>7200</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>0</v>
@@ -1529,7 +1508,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S015-FOD-01</t>
+          <t>S011-WAT-01</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1539,17 +1518,20 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>S015</t>
+          <t>S011</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>1491.941017737513</v>
+        <v>6390.406139995605</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>14400</v>
+        <v>10800</v>
+      </c>
+      <c r="F36" t="n">
+        <v>10800</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>0</v>
@@ -1558,7 +1540,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S011-WAT-01</t>
+          <t>S007-MED-01</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1568,20 +1550,20 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>S011</t>
+          <t>S007</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>6253.936139995606</v>
+        <v>1111.35204227048</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>10800</v>
+        <v>3600</v>
       </c>
       <c r="F37" t="n">
-        <v>10800</v>
+        <v>3600</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>0</v>
@@ -1590,7 +1572,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S007-FOD-01</t>
+          <t>S003-WAT-01</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1600,13 +1582,16 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>S007</t>
+          <t>S003</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>6782.067105977863</v>
+        <v>1568.820027438731</v>
       </c>
       <c r="E38" s="2" t="n">
+        <v>7200</v>
+      </c>
+      <c r="F38" t="n">
         <v>7200</v>
       </c>
       <c r="G38" s="2" t="n">
@@ -1619,7 +1604,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S008-FOD-01</t>
+          <t>S002-MED-01</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1629,17 +1614,20 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>6644.023384496832</v>
+        <v>3513.566990967301</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>10800</v>
+        <v>3600</v>
+      </c>
+      <c r="F39" t="n">
+        <v>3600</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>0</v>
@@ -1648,7 +1636,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S008-MED-01</t>
+          <t>S004-MED-01</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1658,11 +1646,11 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>S004</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>6644.023384496832</v>
+        <v>3991.097814774521</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>7200</v>
@@ -1680,7 +1668,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S008-WAT-01</t>
+          <t>S004-WAT-01</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1690,11 +1678,11 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>S004</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>6644.023384496832</v>
+        <v>3991.097814774521</v>
       </c>
       <c r="E41" s="2" t="n">
         <v>7200</v>
@@ -1712,7 +1700,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S007-MED-01</t>
+          <t>S013-FOD-01</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1722,20 +1710,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>S007</t>
+          <t>S013</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>1111.35204227048</v>
+        <v>3044.000202171553</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>3600</v>
-      </c>
-      <c r="F42" t="n">
-        <v>3600</v>
+        <v>7200</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="H42" s="2" t="n">
         <v>0</v>
@@ -1744,7 +1729,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S003-WAT-01</t>
+          <t>S010-FOD-01</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1754,16 +1739,13 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>S003</t>
+          <t>S010</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>1568.820027438731</v>
+        <v>3450.667856901935</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>7200</v>
-      </c>
-      <c r="F43" t="n">
         <v>7200</v>
       </c>
       <c r="G43" s="2" t="n">
@@ -1776,7 +1758,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S002-HYG-01</t>
+          <t>S006-FOD-01</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1786,17 +1768,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>1451.81119240763</v>
+        <v>6624.97596075492</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>10800</v>
+        <v>7200</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>0</v>
@@ -1805,7 +1787,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S002-WAT-01</t>
+          <t>S006-HYG-01</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1815,20 +1797,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>1451.81119240763</v>
+        <v>6624.97596075492</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>3600</v>
-      </c>
-      <c r="F45" t="n">
-        <v>3600</v>
+        <v>10800</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>0</v>
@@ -1837,27 +1816,27 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S002-WAT-02</t>
+          <t>S005-FOD-01</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Q2-017</t>
+          <t>Q2-018</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>1451.81119240763</v>
+        <v>4867.213262262891</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>3600</v>
+        <v>14400</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H46" s="2" t="n">
         <v>0</v>
@@ -1866,27 +1845,27 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S002-WAT-03</t>
+          <t>S005-HYG-01</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Q2-017</t>
+          <t>Q2-018</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>1451.81119240763</v>
+        <v>4867.213262262891</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>3600</v>
+        <v>18000</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H47" s="2" t="n">
         <v>0</v>
@@ -1895,27 +1874,27 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S002-WAT-04</t>
+          <t>S005-WAT-02</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Q2-017</t>
+          <t>Q2-018</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>1451.81119240763</v>
+        <v>4867.213262262891</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>3600</v>
+        <v>10800</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H48" s="2" t="n">
         <v>0</v>
@@ -1938,7 +1917,7 @@
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>5118.348346241602</v>
+        <v>5466.16528745803</v>
       </c>
       <c r="E49" s="2" t="n">
         <v>10800</v>
@@ -1967,7 +1946,7 @@
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>5118.348346241602</v>
+        <v>5466.16528745803</v>
       </c>
       <c r="E50" s="2" t="n">
         <v>14400</v>
@@ -1996,7 +1975,7 @@
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>5118.348346241602</v>
+        <v>5466.16528745803</v>
       </c>
       <c r="E51" s="2" t="n">
         <v>7200</v>
@@ -2011,27 +1990,27 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S005-FOD-01</t>
+          <t>S007-WAT-02</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Q2-018</t>
+          <t>Q2-019</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S007</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>5720.63037143674</v>
+        <v>1082.553699490212</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>14400</v>
+        <v>3600</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H52" s="2" t="n">
         <v>0</v>
@@ -2040,27 +2019,27 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S005-HYG-01</t>
+          <t>S015-FOD-01</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Q2-018</t>
+          <t>Q2-019</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S015</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>5720.63037143674</v>
+        <v>1473.351017737512</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>18000</v>
+        <v>14400</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>0</v>
@@ -2069,27 +2048,30 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S005-WAT-02</t>
+          <t>S014-MED-01</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Q2-018</t>
+          <t>Q2-020</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S014</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>5720.63037143674</v>
+        <v>2586.240572494324</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>10800</v>
+        <v>7200</v>
+      </c>
+      <c r="F54" t="n">
+        <v>3600</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="H54" s="2" t="n">
         <v>0</v>
@@ -2098,21 +2080,21 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>S008-HYG-01</t>
+          <t>S011-FOD-01</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Q2-019</t>
+          <t>Q2-020</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>S011</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>6674.736384496832</v>
+        <v>3641.992840940934</v>
       </c>
       <c r="E55" s="2" t="n">
         <v>14400</v>
@@ -2127,27 +2109,30 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>S008-WAT-02</t>
+          <t>S011-MED-01</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Q2-019</t>
+          <t>Q2-020</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>S011</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>6674.736384496832</v>
+        <v>3641.992840940934</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>7200</v>
+        <v>10800</v>
+      </c>
+      <c r="F56" t="n">
+        <v>10800</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H56" s="2" t="n">
         <v>0</v>
@@ -2156,30 +2141,27 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>S006-WAT-01</t>
+          <t>S002-HYG-01</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Q2-020</t>
+          <t>Q2-021</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>2524.040960754921</v>
+        <v>2981.486192407631</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>3600</v>
-      </c>
-      <c r="F57" t="n">
-        <v>3600</v>
+        <v>10800</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H57" s="2" t="n">
         <v>0</v>
@@ -2188,23 +2170,26 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>S006-WAT-02</t>
+          <t>S002-WAT-01</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Q2-020</t>
+          <t>Q2-021</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>2524.040960754921</v>
+        <v>2981.486192407631</v>
       </c>
       <c r="E58" s="2" t="n">
+        <v>3600</v>
+      </c>
+      <c r="F58" t="n">
         <v>3600</v>
       </c>
       <c r="G58" s="2" t="n">
@@ -2217,7 +2202,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>S003-FOD-01</t>
+          <t>S002-WAT-02</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2227,17 +2212,17 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>S003</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>6175.922674802335</v>
+        <v>2981.486192407631</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>10800</v>
+        <v>3600</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H59" s="2" t="n">
         <v>0</v>
@@ -2246,7 +2231,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>S003-FOD-02</t>
+          <t>S002-WAT-03</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2256,17 +2241,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>S003</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>6175.922674802335</v>
+        <v>2981.486192407631</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>10800</v>
+        <v>3600</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H60" s="2" t="n">
         <v>0</v>
@@ -2275,7 +2260,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>S003-HYG-01</t>
+          <t>S002-WAT-04</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2285,17 +2270,17 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>S003</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>6175.922674802335</v>
+        <v>2981.486192407631</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>14400</v>
+        <v>3600</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H61" s="2" t="n">
         <v>0</v>
@@ -2304,21 +2289,21 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>S003-WAT-02</t>
+          <t>S001-FOD-01</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Q2-021</t>
+          <t>Q2-022</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>S003</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>6175.922674802335</v>
+        <v>1314.26953866458</v>
       </c>
       <c r="E62" s="2" t="n">
         <v>7200</v>
@@ -2333,21 +2318,21 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>S003-WAT-03</t>
+          <t>S001-FOD-02</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Q2-021</t>
+          <t>Q2-022</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>S003</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>6175.922674802335</v>
+        <v>1314.26953866458</v>
       </c>
       <c r="E63" s="2" t="n">
         <v>7200</v>
@@ -2362,21 +2347,21 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S003-WAT-04</t>
+          <t>S001-FOD-03</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Q2-021</t>
+          <t>Q2-022</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>S003</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>6175.922674802335</v>
+        <v>1314.26953866458</v>
       </c>
       <c r="E64" s="2" t="n">
         <v>7200</v>
@@ -2391,7 +2376,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>S006-FOD-01</t>
+          <t>S001-HYG-02</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2401,17 +2386,17 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>4958.50596075492</v>
+        <v>1314.26953866458</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>7200</v>
+        <v>10800</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H65" s="2" t="n">
         <v>0</v>
@@ -2420,7 +2405,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>S006-HYG-01</t>
+          <t>S001-MED-02</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2430,17 +2415,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>4958.50596075492</v>
+        <v>1314.26953866458</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>10800</v>
+        <v>3600</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="H66" s="2" t="n">
         <v>0</v>
@@ -2449,30 +2434,30 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>S005-WAT-01</t>
+          <t>S001-WAT-01</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Q2-023</t>
+          <t>Q2-022</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>4276.464896432129</v>
+        <v>1314.26953866458</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>10800</v>
+        <v>3600</v>
       </c>
       <c r="F67" t="n">
-        <v>10800</v>
+        <v>3600</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H67" s="2" t="n">
         <v>0</v>
@@ -2481,27 +2466,27 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>S009-FOD-01</t>
+          <t>S001-WAT-02</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Q2-023</t>
+          <t>Q2-022</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>S009</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>4786.904789228012</v>
+        <v>1314.26953866458</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>14400</v>
+        <v>3600</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H68" s="2" t="n">
         <v>0</v>
@@ -2510,12 +2495,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>S001-FOD-01</t>
+          <t>S001-WAT-05</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Q2-024</t>
+          <t>Q2-022</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2527,10 +2512,10 @@
         <v>1314.26953866458</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>7200</v>
+        <v>3600</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H69" s="2" t="n">
         <v>0</v>
@@ -2539,27 +2524,30 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>S001-FOD-02</t>
+          <t>S009-MED-01</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Q2-024</t>
+          <t>Q2-023</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S009</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>1314.26953866458</v>
+        <v>4300.793615915665</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>7200</v>
+        <v>10800</v>
+      </c>
+      <c r="F70" t="n">
+        <v>10800</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H70" s="2" t="n">
         <v>0</v>
@@ -2568,27 +2556,30 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>S001-FOD-03</t>
+          <t>S005-MED-01</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Q2-024</t>
+          <t>Q2-023</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>1314.26953866458</v>
+        <v>4843.566842044883</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>7200</v>
+        <v>10800</v>
+      </c>
+      <c r="F71" t="n">
+        <v>10800</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H71" s="2" t="n">
         <v>0</v>
@@ -2597,21 +2588,21 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>S001-HYG-02</t>
+          <t>S005-WAT-03</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Q2-024</t>
+          <t>Q2-023</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>1314.26953866458</v>
+        <v>4843.566842044883</v>
       </c>
       <c r="E72" s="2" t="n">
         <v>10800</v>
@@ -2626,7 +2617,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>S001-MED-02</t>
+          <t>S013-MED-01</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2636,13 +2627,16 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S013</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>1314.26953866458</v>
+        <v>1116.434202171553</v>
       </c>
       <c r="E73" s="2" t="n">
+        <v>3600</v>
+      </c>
+      <c r="F73" t="n">
         <v>3600</v>
       </c>
       <c r="G73" s="2" t="n">
@@ -2655,7 +2649,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>S001-WAT-01</t>
+          <t>S010-MED-01</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2665,11 +2659,11 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S010</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>1314.26953866458</v>
+        <v>1553.101856901935</v>
       </c>
       <c r="E74" s="2" t="n">
         <v>3600</v>
@@ -2678,7 +2672,7 @@
         <v>3600</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>0</v>
@@ -2687,7 +2681,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>S001-WAT-02</t>
+          <t>S010-WAT-01</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2697,13 +2691,16 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S010</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>1314.26953866458</v>
+        <v>1553.101856901935</v>
       </c>
       <c r="E75" s="2" t="n">
+        <v>3600</v>
+      </c>
+      <c r="F75" t="n">
         <v>3600</v>
       </c>
       <c r="G75" s="2" t="n">
@@ -2716,23 +2713,26 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>S001-WAT-05</t>
+          <t>S013-WAT-01</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Q2-024</t>
+          <t>Q2-025</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S013</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>1314.26953866458</v>
+        <v>2907.577466506123</v>
       </c>
       <c r="E76" s="2" t="n">
+        <v>3600</v>
+      </c>
+      <c r="F76" t="n">
         <v>3600</v>
       </c>
       <c r="G76" s="2" t="n">
@@ -2759,7 +2759,7 @@
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>3007.860341184267</v>
+        <v>3498.21918929102</v>
       </c>
       <c r="E77" s="2" t="n">
         <v>7200</v>
@@ -2788,7 +2788,7 @@
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>3007.860341184267</v>
+        <v>3498.21918929102</v>
       </c>
       <c r="E78" s="2" t="n">
         <v>7200</v>
@@ -2820,7 +2820,7 @@
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>3007.860341184267</v>
+        <v>3498.21918929102</v>
       </c>
       <c r="E79" s="2" t="n">
         <v>3600</v>
@@ -2838,30 +2838,27 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>S013-WAT-01</t>
+          <t>S007-HYG-01</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Q2-025</t>
+          <t>Q2-026</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>S013</t>
+          <t>S007</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>3519.312063969165</v>
+        <v>1112.553699490212</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>3600</v>
-      </c>
-      <c r="F80" t="n">
-        <v>3600</v>
+        <v>10800</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H80" s="2" t="n">
         <v>0</v>
@@ -2870,7 +2867,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>S004-WAT-02</t>
+          <t>S007-WAT-01</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2880,17 +2877,20 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>S004</t>
+          <t>S007</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>4208.567485198306</v>
+        <v>1112.553699490212</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>7200</v>
+        <v>3600</v>
+      </c>
+      <c r="F81" t="n">
+        <v>3600</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H81" s="2" t="n">
         <v>0</v>
